--- a/NN-Fitvermogen/nn.xlsx
+++ b/NN-Fitvermogen/nn.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\NN-Fitvermogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA613116-30DB-4148-B18C-5122FB4C40D9}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CA5DDC-E004-4F75-8EE0-67E5C1D72773}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DC6A66A5-4117-4406-B3CA-45E9AC999DDA}"/>
   </bookViews>
@@ -23,7 +23,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -544,7 +546,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K7" s="3">
+      <c r="K7" s="10">
         <f>SUM(K3:K5)</f>
         <v>2.6587204377389799E-3</v>
       </c>

--- a/NN-Fitvermogen/nn.xlsx
+++ b/NN-Fitvermogen/nn.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\NN-Fitvermogen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gerben\Google Drive\Financieel\IndexFondsen\KeuzeWelkIndexFonds\OnderzoekPerFonds\NN-Fitvermogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CA5DDC-E004-4F75-8EE0-67E5C1D72773}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6949D7F0-0CCB-43FD-849D-3630A040319A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DC6A66A5-4117-4406-B3CA-45E9AC999DDA}"/>
+    <workbookView xWindow="8295" yWindow="3705" windowWidth="28800" windowHeight="15435" xr2:uid="{DC6A66A5-4117-4406-B3CA-45E9AC999DDA}"/>
   </bookViews>
   <sheets>
     <sheet name="NN" sheetId="1" r:id="rId1"/>
@@ -64,12 +64,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="0.000%"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="0.0000%"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;?_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="0.000%"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="0.0000%"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;?_ ;_ @_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -132,37 +132,39 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
-    <cellStyle name="Komma" xfId="2" builtinId="3"/>
-    <cellStyle name="Procent" xfId="1" builtinId="5"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -178,7 +180,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -474,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1CF5CD-3522-4A3D-AF8A-8E57743A5ACD}">
-  <dimension ref="A3:M97"/>
+  <dimension ref="A3:M98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -530,7 +532,7 @@
         <v>177693</v>
       </c>
       <c r="E5" s="2">
-        <f>AVERAGE(B24:C24)/1000</f>
+        <f>AVERAGE(B25:C25)/1000</f>
         <v>2.2315214227798417E-3</v>
       </c>
       <c r="G5" s="3">
@@ -546,7 +548,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K7" s="10">
+      <c r="K7" s="3">
         <f>SUM(K3:K5)</f>
         <v>2.6587204377389799E-3</v>
       </c>
@@ -629,152 +631,166 @@
       <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
+      <c r="B16" s="21">
+        <f>B12/B13</f>
+        <v>6.5999456564107652E-4</v>
+      </c>
+      <c r="C16" s="22">
+        <f>C12/C13</f>
+        <v>4.5577331391664905E-4</v>
+      </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="9">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="9">
         <f>B15/100</f>
         <v>6.5999456564107654E-3</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C18" s="9">
         <f>C15/100</f>
         <v>4.5577331391664904E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="13">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="13">
         <f>B14*0.08%</f>
         <v>0.108</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C19" s="13">
         <f>C14*0.08%</f>
         <v>6.4799999999999996E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B21" s="4">
         <v>2019</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C21" s="4">
         <v>2018</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D21" s="4">
         <v>2017</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E21" s="4">
         <v>2016</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F21" s="4">
         <v>2015</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B22" s="5">
         <v>761</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C22" s="5">
         <v>191</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D22" s="5">
         <v>759</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E22" s="5">
         <v>2922</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F22" s="5">
         <v>2003</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B23" s="5">
         <v>224606</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C23" s="5">
         <v>177693</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D23" s="5">
         <v>216688</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E23" s="5">
         <v>753874</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F23" s="5">
         <v>524800</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B24" s="5">
         <v>152</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C24" s="5">
         <v>-17</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D24" s="5">
         <v>88</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="6">
-        <f>(B21/B22)*1000</f>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="6">
+        <f>(B22/B23)*1000</f>
         <v>3.3881552585416244</v>
       </c>
-      <c r="C24" s="6">
-        <f>(C21/C22)*1000</f>
+      <c r="C25" s="6">
+        <f>(C22/C23)*1000</f>
         <v>1.0748875870180592</v>
       </c>
-      <c r="D24" s="6">
-        <f t="shared" ref="D24:F24" si="0">(D21/D22)*1000</f>
+      <c r="D25" s="6">
+        <f t="shared" ref="D25:F25" si="0">(D22/D23)*1000</f>
         <v>3.5027320386915748</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E25" s="6">
         <f t="shared" si="0"/>
         <v>3.8759792750512685</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F25" s="6">
         <f t="shared" si="0"/>
         <v>3.8166920731707314</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="4"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="2">
+        <f>B22/B23</f>
+        <v>3.3881552585416242E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="4"/>
     </row>
     <row r="33" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C33" s="12"/>
-    </row>
-    <row r="36" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+    </row>
+    <row r="34" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C34" s="12"/>
     </row>
     <row r="37" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C37" s="5"/>
@@ -782,33 +798,28 @@
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
     </row>
     <row r="39" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
     </row>
     <row r="40" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
     </row>
     <row r="41" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="I41" s="11"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
     </row>
     <row r="42" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="10"/>
-      <c r="I42" s="2"/>
+      <c r="I42" s="11"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
@@ -818,83 +829,90 @@
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="10"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="10"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="10"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="10"/>
+    </row>
+    <row r="45" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="3"/>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
       <c r="E51" s="4"/>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B52" s="4"/>
-      <c r="C52" s="5"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
+      <c r="E52" s="4"/>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C53" s="9"/>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="4"/>
-      <c r="C55" s="9"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="5"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C54" s="9"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="4"/>
-      <c r="C56" s="10"/>
+      <c r="C56" s="9"/>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57" s="4"/>
-      <c r="C57" s="9"/>
+      <c r="C57" s="10"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B58" s="4"/>
       <c r="C58" s="9"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C59" s="10"/>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="9"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="10"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="4"/>
-      <c r="C65" s="5"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" s="4"/>
       <c r="C66" s="5"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C67" s="18"/>
-      <c r="E67" s="19"/>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C69" s="17"/>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B72" s="20"/>
+      <c r="B67" s="4"/>
+      <c r="C67" s="5"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C68" s="18"/>
+      <c r="E68" s="19"/>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C70" s="17"/>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B73" s="10"/>
+      <c r="B73" s="20"/>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B74" s="10"/>
@@ -923,8 +941,8 @@
     <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" s="10"/>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B88" s="10"/>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="10"/>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" s="10"/>
@@ -947,8 +965,11 @@
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="10"/>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B97" s="9"/>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="10"/>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
